--- a/Registro pago immediatos.xlsx
+++ b/Registro pago immediatos.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Farmavisa_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AF5999-C40C-4683-BFB5-F53101B5107F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19D87530-3324-408C-BD81-BF0877675923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="874" xr2:uid="{BEA16B71-FE3A-4F3E-BD5F-E87CB848FD8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="10" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -246,8 +255,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -323,34 +332,33 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares 2" xfId="3" xr:uid="{4D0EC9AE-4342-456D-B9DB-74CB1208F25A}"/>
@@ -677,590 +685,590 @@
   <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="43.28515625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="13" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="43.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="2" customWidth="1"/>
     <col min="6" max="8" width="12" style="2" customWidth="1"/>
     <col min="9" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="7">
+      <c r="A2" s="4">
         <v>46174</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="7">
         <v>657600</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="11">
+      <c r="A3" s="8">
         <v>46174</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="9">
         <v>75000</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="11">
+      <c r="A4" s="8">
         <v>46175</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="9">
         <v>50000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="11">
+      <c r="A5" s="8">
         <v>46175</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="9">
         <v>67000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="11">
+      <c r="A6" s="8">
         <v>46175</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="9">
         <v>190000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="11">
+      <c r="A7" s="8">
         <v>46176</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="9">
         <v>102000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="11">
+      <c r="A8" s="8">
         <v>46176</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="9">
         <v>693000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
+      <c r="A9" s="8">
         <v>46176</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="9">
         <v>39000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="11">
+      <c r="A10" s="8">
         <v>46178</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="9">
         <v>91700</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
+      <c r="A11" s="8">
         <v>46179</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="9">
         <v>69800</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="11">
+      <c r="A12" s="8">
         <v>46180</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="9">
         <v>10000</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="11">
+      <c r="A13" s="8">
         <v>46181</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="9">
         <v>21000</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="11">
+      <c r="A14" s="8">
         <v>46181</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="9">
         <v>34000</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="11">
+      <c r="A15" s="8">
         <v>46182</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="9">
         <v>67800</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="11">
+      <c r="A16" s="8">
         <v>46183</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="9">
         <v>110000</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="11">
+      <c r="A17" s="8">
         <v>46186</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="9">
         <v>83800</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="11">
+      <c r="A18" s="8">
         <v>46188</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="9">
         <v>100000</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="11">
+      <c r="A19" s="8">
         <v>46188</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="9">
         <v>100000</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="11">
+      <c r="A20" s="8">
         <v>46189</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="9">
         <v>29500</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="11">
+      <c r="A21" s="8">
         <v>46190</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="9">
         <v>18000</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="11">
+      <c r="A22" s="8">
         <v>46191</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="9">
         <v>38000</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="11">
+      <c r="A23" s="8">
         <v>46191</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="9">
         <v>112500</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="11">
+      <c r="A24" s="8">
         <v>46191</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="9">
         <v>38000</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="11">
+      <c r="A25" s="8">
         <v>46192</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="B25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="9">
         <v>30000</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="11">
+      <c r="A26" s="8">
         <v>46196</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="8" t="s">
+      <c r="B26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="9">
         <v>255950</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="11">
+      <c r="A27" s="8">
         <v>46198</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="8" t="s">
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="9">
         <v>1543000</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="11">
+      <c r="A28" s="8">
         <v>46198</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="B28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="9">
         <v>800000</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="11">
+      <c r="A29" s="8">
         <v>46199</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="8" t="s">
+      <c r="B29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="9">
         <v>32000</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="11">
+      <c r="A30" s="8">
         <v>46199</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="B30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="9">
         <v>55900</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="11">
+      <c r="A31" s="8">
         <v>46200</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="9">
         <v>30000</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="11">
+      <c r="A32" s="8">
         <v>46203</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="8" t="s">
+      <c r="B32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="9">
         <v>100000</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
+      <c r="A33" s="11">
         <v>46204</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="8" t="s">
+      <c r="B33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="9">
         <v>192500</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="11">
+      <c r="A34" s="8">
         <v>46210</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="8" t="s">
+      <c r="B34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="9">
         <v>29000</v>
       </c>
       <c r="L34" s="2">
@@ -1268,90 +1276,90 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="11">
+      <c r="A35" s="8">
         <v>46210</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="8" t="s">
+      <c r="B35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="9">
         <v>147100</v>
       </c>
-      <c r="L35" s="5">
+      <c r="L35" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="11">
+      <c r="A36" s="8">
         <v>46210</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="8" t="s">
+      <c r="B36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="9">
         <v>187300</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="11">
+      <c r="A37" s="8">
         <v>46213</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="8" t="s">
+      <c r="B37" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="9">
         <v>110000</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="11">
+      <c r="A38" s="8">
         <v>46213</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="8" t="s">
+      <c r="B38" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="9">
         <v>75800</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="11">
+      <c r="A39" s="8">
         <v>46218</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="8" t="s">
+      <c r="B39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="9">
         <v>236500</v>
       </c>
       <c r="F39" s="2" t="s">
@@ -1359,616 +1367,616 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="11">
+      <c r="A40" s="8">
         <v>46220</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="8" t="s">
+      <c r="B40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E40" s="12">
+      <c r="E40" s="9">
         <v>100000</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="11">
+      <c r="A41" s="8">
         <v>46222</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="8" t="s">
+      <c r="B41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="9">
         <v>19000</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="11">
+      <c r="A42" s="8">
         <v>46221</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="8" t="s">
+      <c r="B42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="9">
         <v>88850</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="11">
+      <c r="A43" s="8">
         <v>46224</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="8" t="s">
+      <c r="B43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="9">
         <v>8000</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" s="11">
+      <c r="A44" s="8">
         <v>46227</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="8" t="s">
+      <c r="B44" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E44" s="12">
+      <c r="E44" s="9">
         <v>66900</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="11">
+      <c r="A45" s="8">
         <v>46226</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" s="8" t="s">
+      <c r="B45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="9">
         <v>188800</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="11">
+      <c r="A46" s="8">
         <v>46228</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="8" t="s">
+      <c r="B46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E46" s="12">
+      <c r="E46" s="9">
         <v>125000</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" s="11">
+      <c r="A47" s="8">
         <v>46228</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" s="8" t="s">
+      <c r="B47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E47" s="12">
+      <c r="E47" s="9">
         <v>22500</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="11">
+      <c r="A48" s="8">
         <v>46231</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="8" t="s">
+      <c r="B48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="12">
+      <c r="E48" s="9">
         <v>108400</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="11">
+      <c r="A49" s="8">
         <v>46233</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="8" t="s">
+      <c r="B49" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="9">
         <v>63000</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
+      <c r="A50" s="11">
         <v>46237</v>
       </c>
-      <c r="B50" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" s="8" t="s">
+      <c r="B50" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E50" s="12">
+      <c r="E50" s="9">
         <v>95000</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="11">
+      <c r="A51" s="8">
         <v>46237</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="8" t="s">
+      <c r="B51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E51" s="9">
         <v>236800</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="11">
+      <c r="A52" s="8">
         <v>46237</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C52" s="8" t="s">
+      <c r="B52" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="12">
+      <c r="E52" s="9">
         <v>273600</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="11">
+      <c r="A53" s="8">
         <v>46238</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" s="8" t="s">
+      <c r="B53" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E53" s="12">
+      <c r="E53" s="9">
         <v>69200</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="11">
+      <c r="A54" s="8">
         <v>46238</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C54" s="8" t="s">
+      <c r="B54" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E54" s="12">
+      <c r="E54" s="9">
         <v>118200</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="11">
+      <c r="A55" s="8">
         <v>46240</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" s="8" t="s">
+      <c r="B55" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="12">
+      <c r="E55" s="9">
         <v>87000</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="11">
+      <c r="A56" s="8">
         <v>46242</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="8" t="s">
+      <c r="B56" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E56" s="12">
+      <c r="E56" s="9">
         <v>35000</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="11">
+      <c r="A57" s="8">
         <v>46242</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C57" s="8" t="s">
+      <c r="B57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E57" s="12">
+      <c r="E57" s="9">
         <v>69300</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="11">
+      <c r="A58" s="8">
         <v>46245</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C58" s="8" t="s">
+      <c r="B58" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E58" s="12">
+      <c r="E58" s="9">
         <v>162933</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="11">
+      <c r="A59" s="8">
         <v>46245</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C59" s="8" t="s">
+      <c r="B59" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E59" s="12">
+      <c r="E59" s="9">
         <v>187900</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="11">
+      <c r="A60" s="8">
         <v>46247</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="8" t="s">
+      <c r="B60" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E60" s="12">
+      <c r="E60" s="9">
         <f>63700+126000</f>
         <v>189700</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="11">
+      <c r="A61" s="8">
         <v>46248</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C61" s="8" t="s">
+      <c r="B61" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="12">
+      <c r="E61" s="9">
         <v>182000</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="11">
+      <c r="A62" s="8">
         <v>46248</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C62" s="8" t="s">
+      <c r="B62" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E62" s="12">
+      <c r="E62" s="9">
         <v>55900</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="11">
+      <c r="A63" s="8">
         <v>46250</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="8" t="s">
+      <c r="B63" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E63" s="12">
+      <c r="E63" s="9">
         <v>36000</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="11">
+      <c r="A64" s="8">
         <v>46250</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C64" s="8" t="s">
+      <c r="B64" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E64" s="12">
+      <c r="E64" s="9">
         <v>60000</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="11">
+      <c r="A65" s="8">
         <v>46258</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" s="8" t="s">
+      <c r="B65" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D65" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E65" s="12">
+      <c r="E65" s="9">
         <v>162000</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="11">
+      <c r="A66" s="8">
         <v>46259</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66" s="8" t="s">
+      <c r="B66" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E66" s="12">
+      <c r="E66" s="9">
         <v>10000</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="11">
+      <c r="A67" s="8">
         <v>46261</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67" s="8" t="s">
+      <c r="B67" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E67" s="12">
+      <c r="E67" s="9">
         <v>56000</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="11">
+      <c r="A68" s="8">
         <v>46262</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C68" s="8" t="s">
+      <c r="B68" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E68" s="12">
+      <c r="E68" s="9">
         <v>600000</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="11">
+      <c r="A69" s="8">
         <v>46262</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C69" s="8" t="s">
+      <c r="B69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="9">
         <v>10000</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="11">
+      <c r="A70" s="8">
         <v>46265</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C70" s="8" t="s">
+      <c r="B70" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E70" s="12">
+      <c r="E70" s="9">
         <v>44000</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="12">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="8"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="12">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="8"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="12">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="8"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="12">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="8"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="12">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="8"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="12">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="8"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="12">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="8"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="12">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="8"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="12">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E80" s="12"/>
+      <c r="E80" s="9"/>
     </row>
     <row r="81" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E81" s="1">
